--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/pc_summary_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/pc_summary_statistics.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -781,32 +781,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>7.361126679076392e-09</v>
+        <v>3.900380859099747e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>7.361126679076392e-09</v>
+        <v>2.23462303242758e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.333212455040135e-09</v>
+        <v>5.057560661945904e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>3.589975986608956e-09</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1.113227737154383e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.234596061958361e-06</v>
+        <v>3.303475161404527e-06</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5.965445949021894e-08</v>
+        <v>3.160862760546667e-08</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1103,40 +1103,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>1.763197857844507e-05</v>
+        <v>3.386858972780748e-05</v>
       </c>
       <c r="G13" t="n">
         <v>1.763197857844507e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>4.442325701774602e-06</v>
+        <v>3.503227980408492e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>1.449077995048096e-05</v>
+        <v>1.399746305885704e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.077317720640918e-05</v>
+        <v>8.621293869548276e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002686642718627503</v>
+        <v>0.005160668700768165</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.003x</t>
+          <t>0.005x</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.0001148505548663055</v>
+        <v>0.0002206120150085267</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1425,40 +1425,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>6.156413849967099e-06</v>
+        <v>1.133011736146164e-05</v>
       </c>
       <c r="G19" t="n">
-        <v>6.156413849967099e-06</v>
+        <v>6.249272118858353e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>8.308195579658827e-07</v>
+        <v>1.062776780653531e-05</v>
       </c>
       <c r="I19" t="n">
         <v>5.568935706587013e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>6.743891993347184e-06</v>
+        <v>2.725298950154282e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001108353683346064</v>
+        <v>0.00203978771024081</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.001x</t>
+          <t>0.002x</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3.988362770332486e-05</v>
+        <v>7.340087812354076e-05</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1747,40 +1747,40 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>1.018854433568424e-05</v>
+        <v>5.262023389576357e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>1.018854433568424e-05</v>
+        <v>3.702951722746446e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>4.506088177060299e-06</v>
+        <v>6.255572233368532e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>7.002258829060379e-06</v>
+        <v>2.673602705044273e-07</v>
       </c>
       <c r="J25" t="n">
         <v>1.337482984230811e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002956765928826241</v>
+        <v>0.001527065198165157</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.003x</t>
+          <t>0.002x</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>8.28203477816779e-05</v>
+        <v>4.277378522402727e-05</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2069,32 +2069,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>5.00432840520515e-06</v>
+        <v>3.278834798677767e-06</v>
       </c>
       <c r="G31" t="n">
-        <v>5.00432840520515e-06</v>
+        <v>3.74107244799273e-06</v>
       </c>
       <c r="H31" t="n">
-        <v>5.894651698845204e-07</v>
+        <v>2.298905557719005e-06</v>
       </c>
       <c r="I31" t="n">
-        <v>4.587513586306526e-06</v>
+        <v>2.120510746218334e-07</v>
       </c>
       <c r="J31" t="n">
         <v>5.421143224103775e-06</v>
       </c>
       <c r="K31" t="n">
-        <v>0.001067351273704205</v>
+        <v>0.0006993283044722396</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>3.67312022670244e-05</v>
+        <v>2.406627511997868e-05</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2391,32 +2391,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>1.220059353188834e-08</v>
+        <v>6.134066203306145e-09</v>
       </c>
       <c r="G37" t="n">
-        <v>1.220059353188834e-08</v>
+        <v>5.284376672831872e-09</v>
       </c>
       <c r="H37" t="n">
-        <v>2.498799308228314e-09</v>
+        <v>7.152252239580171e-09</v>
       </c>
       <c r="I37" t="n">
-        <v>1.043367559621584e-08</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>1.396751146756083e-08</v>
       </c>
       <c r="K37" t="n">
-        <v>1.487472712866939e-05</v>
+        <v>7.478534607754445e-06</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1.028403647291798e-07</v>
+        <v>5.170482927508057e-08</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2713,32 +2713,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>9.708958600545967e-09</v>
+        <v>5.166899415143878e-09</v>
       </c>
       <c r="G43" t="n">
-        <v>9.708958600545967e-09</v>
+        <v>4.767660144515841e-09</v>
       </c>
       <c r="H43" t="n">
-        <v>2.012876709525379e-09</v>
+        <v>5.396101365737403e-09</v>
       </c>
       <c r="I43" t="n">
-        <v>8.285639829548106e-09</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>1.113227737154383e-08</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0001369271755830374</v>
+        <v>7.286970441891828e-05</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1.998313737519753e-07</v>
+        <v>1.063459687744902e-07</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -3035,44 +3035,44 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>1.868495779843594e-05</v>
+        <v>3.581160335916206e-05</v>
       </c>
       <c r="G49" t="n">
-        <v>1.868495779843594e-05</v>
+        <v>2.021836817535139e-05</v>
       </c>
       <c r="H49" t="n">
-        <v>2.953188207966466e-06</v>
+        <v>3.364728435087913e-05</v>
       </c>
       <c r="I49" t="n">
         <v>1.65967383904627e-05</v>
       </c>
       <c r="J49" t="n">
-        <v>2.077317720640918e-05</v>
+        <v>8.621293869548276e-05</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02808720436417413</v>
+        <v>0.05383195579075518</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.028x</t>
+          <t>0.054x</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.0003145261079706732</v>
+        <v>0.0006028209614521889</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.000x</t>
+          <t>0.001x</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -3357,40 +3357,40 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>7.842509056765815e-06</v>
+        <v>1.240544285621729e-05</v>
       </c>
       <c r="G55" t="n">
         <v>7.842509056765815e-06</v>
       </c>
       <c r="H55" t="n">
-        <v>1.55367915094113e-06</v>
+        <v>9.953925542481741e-06</v>
       </c>
       <c r="I55" t="n">
-        <v>6.743891993347184e-06</v>
+        <v>6.683763809794704e-06</v>
       </c>
       <c r="J55" t="n">
-        <v>8.941126120184445e-06</v>
+        <v>2.725298950154282e-05</v>
       </c>
       <c r="K55" t="n">
-        <v>0.01272410337639257</v>
+        <v>0.02012724960722389</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.013x</t>
+          <t>0.020x</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.0001338895335906799</v>
+        <v>0.0002117892304595859</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3679,40 +3679,40 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>1.020703293032152e-05</v>
+        <v>6.72572139199815e-06</v>
       </c>
       <c r="G61" t="n">
-        <v>1.020703293032152e-05</v>
+        <v>6.630347727590031e-06</v>
       </c>
       <c r="H61" t="n">
-        <v>4.479941355775052e-06</v>
+        <v>5.362637507170851e-06</v>
       </c>
       <c r="I61" t="n">
-        <v>7.039236018334921e-06</v>
+        <v>2.673602705044273e-07</v>
       </c>
       <c r="J61" t="n">
         <v>1.337482984230811e-05</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01656282260535741</v>
+        <v>0.01091374261934648</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0.017x</t>
+          <t>0.011x</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.0001638332726423756</v>
+        <v>0.0001079546773341488</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -4001,40 +4001,40 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>4.141023345404901e-06</v>
+        <v>2.597209775572393e-06</v>
       </c>
       <c r="G67" t="n">
-        <v>4.141023345404901e-06</v>
+        <v>2.377822401781981e-06</v>
       </c>
       <c r="H67" t="n">
-        <v>1.810362893919349e-06</v>
+        <v>2.177657642252956e-06</v>
       </c>
       <c r="I67" t="n">
-        <v>2.860903466706027e-06</v>
+        <v>2.120510746218334e-07</v>
       </c>
       <c r="J67" t="n">
         <v>5.421143224103775e-06</v>
       </c>
       <c r="K67" t="n">
-        <v>0.007826814336288726</v>
+        <v>0.004908902223011159</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0.008x</t>
+          <t>0.005x</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>6.644480481044054e-05</v>
+        <v>4.16735386872836e-05</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>within epitope within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>within epitope across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>within strain across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>across strain across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -4323,32 +4323,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pre-Immune Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
-        <v>1.62127355094416e-08</v>
+        <v>8.152577119053574e-09</v>
       </c>
       <c r="G73" t="n">
-        <v>1.62127355094416e-08</v>
+        <v>7.076174462445966e-09</v>
       </c>
       <c r="H73" t="n">
-        <v>3.175226290593917e-09</v>
+        <v>9.486196244225345e-09</v>
       </c>
       <c r="I73" t="n">
-        <v>1.396751146756083e-08</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>1.845795955132237e-08</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0001989488653890196</v>
+        <v>0.0001000414746103542</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>3.118785496515796e-07</v>
+        <v>1.568281877128245e-07</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/pc_summary_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/pc_summary_statistics.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="D72" t="n">

--- a/Final_Figures_and_Sheets_Singleset_NT_Dedup/pc_summary_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Singleset_NT_Dedup/pc_summary_statistics.xlsx
@@ -2504,16 +2504,16 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0005304555246482213</v>
+        <v>0.0003248646286759551</v>
       </c>
       <c r="G39" t="n">
-        <v>1.262491385739171e-05</v>
+        <v>1.119467312673937e-05</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00229977818491918</v>
+        <v>0.001746226995191943</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2522,19 +2522,19 @@
         <v>0.01373626373626374</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01091792236077905</v>
+        <v>0.006686416916855625</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.011x</t>
+          <t>0.007x</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.01091792236077905</v>
+        <v>0.006686416916855625</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.011x</t>
+          <t>0.007x</t>
         </is>
       </c>
     </row>
@@ -2576,11 +2576,11 @@
         <v>0.01373626373626374</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2858084172642463</v>
+        <v>0.4666825518884349</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.286x</t>
+          <t>0.467x</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2826,16 +2826,16 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00439793150927935</v>
+        <v>0.002630360999215243</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0003836815596684018</v>
+        <v>0.0002033787108413974</v>
       </c>
       <c r="H45" t="n">
-        <v>0.01724774177436068</v>
+        <v>0.01312308503089243</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2844,19 +2844,19 @@
         <v>0.1025641025641026</v>
       </c>
       <c r="K45" t="n">
-        <v>0.07403090205807215</v>
+        <v>0.04427717828242959</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.074x</t>
+          <t>0.044x</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.07403090205807215</v>
+        <v>0.04427717828242959</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.074x</t>
+          <t>0.044x</t>
         </is>
       </c>
     </row>
@@ -2898,11 +2898,11 @@
         <v>0.1025641025641026</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2880524624554786</v>
+        <v>0.4816202039706379</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.288x</t>
+          <t>0.482x</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3148,16 +3148,16 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F51" t="n">
-        <v>0.002864215032654163</v>
+        <v>0.001769551992824574</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0001631125890019754</v>
+        <v>0.0001497262149212868</v>
       </c>
       <c r="H51" t="n">
-        <v>0.01157690363689863</v>
+        <v>0.008793869231879026</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3166,19 +3166,19 @@
         <v>0.06818181818181818</v>
       </c>
       <c r="K51" t="n">
-        <v>0.04889868944360867</v>
+        <v>0.03021029230171474</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.049x</t>
+          <t>0.030x</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.04889868944360867</v>
+        <v>0.03021029230171474</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.049x</t>
+          <t>0.030x</t>
         </is>
       </c>
     </row>
@@ -3220,11 +3220,11 @@
         <v>0.06818181818181818</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4308820361548683</v>
+        <v>0.6974300897966074</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.431x</t>
+          <t>0.697x</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3470,16 +3470,16 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00492820722299895</v>
+        <v>0.00284497731607858</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0001434073597594105</v>
+        <v>8.907621447814374e-05</v>
       </c>
       <c r="H57" t="n">
-        <v>0.02132557325996759</v>
+        <v>0.016205419471924</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -3488,19 +3488,19 @@
         <v>0.126984126984127</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0791027444621244</v>
+        <v>0.04566478304403725</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.079x</t>
+          <t>0.046x</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.0791027444621244</v>
+        <v>0.04566478304403725</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0.079x</t>
+          <t>0.046x</t>
         </is>
       </c>
     </row>
@@ -3542,11 +3542,11 @@
         <v>0.126984126984127</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2699252084868504</v>
+        <v>0.4675774933657332</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0.270x</t>
+          <t>0.468x</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -3792,16 +3792,16 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F63" t="n">
-        <v>0.002845411948225312</v>
+        <v>0.001641808749204527</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0001069952558471885</v>
+        <v>2.264490954351835e-05</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01164278086572711</v>
+        <v>0.008859361494750202</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3810,19 +3810,19 @@
         <v>0.06818181818181818</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04565606753096921</v>
+        <v>0.02634364812215319</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0.046x</t>
+          <t>0.026x</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.04565606753096921</v>
+        <v>0.02634364812215319</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>0.046x</t>
+          <t>0.026x</t>
         </is>
       </c>
     </row>
@@ -3864,11 +3864,11 @@
         <v>0.06818181818181818</v>
       </c>
       <c r="K64" t="n">
-        <v>0.3743806691789851</v>
+        <v>0.6488375882895034</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.374x</t>
+          <t>0.649x</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -4114,16 +4114,16 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0005437009504611307</v>
+        <v>0.0003538867847661307</v>
       </c>
       <c r="G69" t="n">
-        <v>5.151224870491624e-06</v>
+        <v>1.17090534401199e-05</v>
       </c>
       <c r="H69" t="n">
-        <v>0.002212358351326903</v>
+        <v>0.001683560986107931</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -4132,19 +4132,19 @@
         <v>0.01316391941391941</v>
       </c>
       <c r="K69" t="n">
-        <v>0.01045897922502056</v>
+        <v>0.006807592531775221</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0.010x</t>
+          <t>0.007x</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0.01045897922502056</v>
+        <v>0.006807592531775221</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>0.010x</t>
+          <t>0.007x</t>
         </is>
       </c>
     </row>
@@ -4186,11 +4186,11 @@
         <v>0.01316391941391941</v>
       </c>
       <c r="K70" t="n">
-        <v>0.3037463261451495</v>
+        <v>0.4666666666666668</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0.304x</t>
+          <t>0.467x</t>
         </is>
       </c>
       <c r="M70" t="n">
